--- a/metadata/Oulanka_ACAP_study_site.xlsx
+++ b/metadata/Oulanka_ACAP_study_site.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://valtion-my.sharepoint.com/personal/tommi_valikangas_luke_fi/Documents/Oulanka_MG_MT_project_2009164/Metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lukefinland-my.sharepoint.com/personal/tommi_valikangas_luke_fi/Documents/Oulanka_MG_MT_project_2009164/Manuscript/scripts_fems_revision_published_git/scripts_published_cleaned/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{3FF7BBBC-8EE0-4012-955F-03FEB53B3112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1D40A46-8EB0-4DB2-94D8-4C5C623C6D18}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{3FF7BBBC-8EE0-4012-955F-03FEB53B3112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59AEE363-2275-47A2-8EA8-3B243CC4AC77}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fen site" sheetId="1" r:id="rId1"/>
-    <sheet name="mineral forest site" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="59">
   <si>
     <t>Block</t>
   </si>
@@ -212,138 +211,6 @@
   </si>
   <si>
     <t>P36</t>
-  </si>
-  <si>
-    <t>Explanation_1</t>
-  </si>
-  <si>
-    <t>Explanation_2</t>
-  </si>
-  <si>
-    <t>Short code mineral layer</t>
-  </si>
-  <si>
-    <t>shadow</t>
-  </si>
-  <si>
-    <t>Vaccinium</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>M3</t>
-  </si>
-  <si>
-    <t>light</t>
-  </si>
-  <si>
-    <t>Lichen</t>
-  </si>
-  <si>
-    <t>M4</t>
-  </si>
-  <si>
-    <t>M5</t>
-  </si>
-  <si>
-    <t>M6</t>
-  </si>
-  <si>
-    <t>M7</t>
-  </si>
-  <si>
-    <t>M8</t>
-  </si>
-  <si>
-    <t>M9</t>
-  </si>
-  <si>
-    <t>M10</t>
-  </si>
-  <si>
-    <t>M11</t>
-  </si>
-  <si>
-    <t>M12</t>
-  </si>
-  <si>
-    <t>M13</t>
-  </si>
-  <si>
-    <t>M14</t>
-  </si>
-  <si>
-    <t>M15</t>
-  </si>
-  <si>
-    <t>M16</t>
-  </si>
-  <si>
-    <t>M17</t>
-  </si>
-  <si>
-    <t>M18</t>
-  </si>
-  <si>
-    <t>Lichen-like</t>
-  </si>
-  <si>
-    <t>M19</t>
-  </si>
-  <si>
-    <t>M20</t>
-  </si>
-  <si>
-    <t>M21</t>
-  </si>
-  <si>
-    <t>M22</t>
-  </si>
-  <si>
-    <t>M23</t>
-  </si>
-  <si>
-    <t>M24</t>
-  </si>
-  <si>
-    <t>M25</t>
-  </si>
-  <si>
-    <t>M26</t>
-  </si>
-  <si>
-    <t>M27</t>
-  </si>
-  <si>
-    <t>M28</t>
-  </si>
-  <si>
-    <t>M29</t>
-  </si>
-  <si>
-    <t>M30</t>
-  </si>
-  <si>
-    <t>M31</t>
-  </si>
-  <si>
-    <t>M32</t>
-  </si>
-  <si>
-    <t>M33</t>
-  </si>
-  <si>
-    <t>M34</t>
-  </si>
-  <si>
-    <t>M35</t>
-  </si>
-  <si>
-    <t>M36</t>
   </si>
 </sst>
 </file>
@@ -412,9 +279,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-teema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022 -teema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -452,7 +319,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -558,7 +425,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -700,7 +567,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1687,1097 +1554,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="13" max="14" width="12.109375" customWidth="1"/>
-    <col min="15" max="15" width="9.88671875" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="9.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
-      </c>
-      <c r="G3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" t="s">
-        <v>63</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" t="s">
-        <v>63</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>4</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" t="s">
-        <v>15</v>
-      </c>
-      <c r="I15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E16" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" t="s">
-        <v>12</v>
-      </c>
-      <c r="I18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>6</v>
-      </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20">
-        <v>19</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" t="s">
-        <v>84</v>
-      </c>
-      <c r="G20" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="I20" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>1</v>
-      </c>
-      <c r="B21">
-        <v>20</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" t="s">
-        <v>12</v>
-      </c>
-      <c r="I21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" t="s">
-        <v>67</v>
-      </c>
-      <c r="F22" t="s">
-        <v>84</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>2</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" t="s">
-        <v>14</v>
-      </c>
-      <c r="H23" t="s">
-        <v>15</v>
-      </c>
-      <c r="I23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>2</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" t="s">
-        <v>11</v>
-      </c>
-      <c r="H24" t="s">
-        <v>12</v>
-      </c>
-      <c r="I24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>2</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" t="s">
-        <v>62</v>
-      </c>
-      <c r="F25" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>3</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26" t="s">
-        <v>67</v>
-      </c>
-      <c r="F26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G26" t="s">
-        <v>11</v>
-      </c>
-      <c r="H26" t="s">
-        <v>12</v>
-      </c>
-      <c r="I26" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>3</v>
-      </c>
-      <c r="B27">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H27" t="s">
-        <v>15</v>
-      </c>
-      <c r="I27" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>3</v>
-      </c>
-      <c r="B28">
-        <v>27</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" t="s">
-        <v>67</v>
-      </c>
-      <c r="F28" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>4</v>
-      </c>
-      <c r="B29">
-        <v>28</v>
-      </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>4</v>
-      </c>
-      <c r="B30">
-        <v>29</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" t="s">
-        <v>84</v>
-      </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
-      <c r="H30" t="s">
-        <v>12</v>
-      </c>
-      <c r="I30" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>4</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G31" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>5</v>
-      </c>
-      <c r="B32">
-        <v>31</v>
-      </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" t="s">
-        <v>62</v>
-      </c>
-      <c r="F32" t="s">
-        <v>63</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" t="s">
-        <v>18</v>
-      </c>
-      <c r="I32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>5</v>
-      </c>
-      <c r="B33">
-        <v>32</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F33" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" t="s">
-        <v>15</v>
-      </c>
-      <c r="I33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>5</v>
-      </c>
-      <c r="B34">
-        <v>33</v>
-      </c>
-      <c r="C34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" t="s">
-        <v>11</v>
-      </c>
-      <c r="H34" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>6</v>
-      </c>
-      <c r="B35">
-        <v>34</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" t="s">
-        <v>62</v>
-      </c>
-      <c r="F35" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>6</v>
-      </c>
-      <c r="B36">
-        <v>35</v>
-      </c>
-      <c r="C36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" t="s">
-        <v>62</v>
-      </c>
-      <c r="F36" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>6</v>
-      </c>
-      <c r="B37">
-        <v>36</v>
-      </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F37" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37" t="s">
-        <v>11</v>
-      </c>
-      <c r="H37" t="s">
-        <v>12</v>
-      </c>
-      <c r="I37" t="s">
-        <v>102</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -2785,15 +1561,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010033FF5D13B29E7C4B88EA59A1A74D5A6E" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8c225aa35fe82e80f9f37cf8d382a81e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8003753c-1cdd-4070-b686-eecc7444231c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0c6508fca123007d8e91c7eee575afba" ns2:_="">
     <xsd:import namespace="8003753c-1cdd-4070-b686-eecc7444231c"/>
@@ -2931,6 +1698,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9400D7F1-991D-45D1-8F65-A7363A55564D}">
   <ds:schemaRefs>
@@ -2941,14 +1717,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC88886-3E39-472B-BF14-A63C3B2D1DD8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6899309A-A65E-4055-9D28-76496528810A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2964,4 +1732,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAC88886-3E39-472B-BF14-A63C3B2D1DD8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>